--- a/Mumbai-March-2026.xlsx
+++ b/Mumbai-March-2026.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="140">
   <si>
     <t>Sr. No</t>
   </si>
@@ -307,28 +307,28 @@
     <t>MH02GH2432</t>
   </si>
   <si>
-    <t>Crysta</t>
-  </si>
-  <si>
-    <t>Etios</t>
-  </si>
-  <si>
-    <t>HYRIDER</t>
-  </si>
-  <si>
-    <t>Fortuner</t>
-  </si>
-  <si>
-    <t>CITRON</t>
+    <t>CRYSTA</t>
+  </si>
+  <si>
+    <t>ETIOS</t>
+  </si>
+  <si>
+    <t>HYRYDER</t>
+  </si>
+  <si>
+    <t>FORTUNER</t>
+  </si>
+  <si>
+    <t>CITROEN</t>
   </si>
   <si>
     <t>DZIRE</t>
   </si>
   <si>
-    <t>BYD</t>
-  </si>
-  <si>
-    <t>MG EV</t>
+    <t>BYD E6</t>
+  </si>
+  <si>
+    <t>MG ZS EV</t>
   </si>
   <si>
     <t>CAMRY</t>
@@ -337,13 +337,13 @@
     <t>INVICTO</t>
   </si>
   <si>
-    <t>Hycross</t>
-  </si>
-  <si>
-    <t>Merc E</t>
-  </si>
-  <si>
-    <t>5 Series</t>
+    <t>HYCROSS</t>
+  </si>
+  <si>
+    <t>MERCEDES E</t>
+  </si>
+  <si>
+    <t>5 SERIES</t>
   </si>
   <si>
     <t>URBANIA</t>
@@ -397,7 +397,7 @@
     <t>17/10/2023</t>
   </si>
   <si>
-    <t>-</t>
+    <t>14/04/2023</t>
   </si>
   <si>
     <t>27/05/2025</t>
@@ -416,6 +416,9 @@
   </si>
   <si>
     <t>27/06/2025</t>
+  </si>
+  <si>
+    <t>16/03/2026</t>
   </si>
   <si>
     <t>22/04/2025</t>
@@ -5612,7 +5615,7 @@
         <v>107</v>
       </c>
       <c r="G61" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="H61">
         <v>84</v>
@@ -5692,7 +5695,7 @@
         <v>107</v>
       </c>
       <c r="G62" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="H62">
         <v>91</v>
@@ -5772,7 +5775,7 @@
         <v>108</v>
       </c>
       <c r="G63" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H63">
         <v>8797</v>
@@ -5852,7 +5855,7 @@
         <v>109</v>
       </c>
       <c r="G64" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H64">
         <v>55544</v>
@@ -5932,7 +5935,7 @@
         <v>110</v>
       </c>
       <c r="G65" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H65">
         <v>71641</v>
@@ -6012,7 +6015,7 @@
         <v>110</v>
       </c>
       <c r="G66" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H66">
         <v>68878</v>
@@ -6092,7 +6095,7 @@
         <v>110</v>
       </c>
       <c r="G67" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H67">
         <v>54548</v>
@@ -6172,7 +6175,7 @@
         <v>110</v>
       </c>
       <c r="G68" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H68">
         <v>15620</v>
@@ -6252,7 +6255,7 @@
         <v>111</v>
       </c>
       <c r="G69" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H69">
         <v>18491</v>
@@ -6332,7 +6335,7 @@
         <v>111</v>
       </c>
       <c r="G70" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H70">
         <v>38886</v>
